--- a/data/macro/Japan/Japan Interest Rate.xlsx
+++ b/data/macro/Japan/Japan Interest Rate.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\Japan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\macro\Japan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02F4E05-F6E5-41CB-AD20-DCFF0ED6534A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F15825-CD7F-4726-B9BF-19C4ED4A7361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BD32588E-2B16-4C89-A5B1-1458B27ABC9F}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="17280" windowHeight="10690" xr2:uid="{BD32588E-2B16-4C89-A5B1-1458B27ABC9F}"/>
   </bookViews>
   <sheets>
-    <sheet name="JP_interest" sheetId="1" r:id="rId1"/>
+    <sheet name="BOJDTR" sheetId="1" r:id="rId1"/>
     <sheet name="info" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -75,21 +75,21 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -98,7 +98,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -115,6 +115,15 @@
       <color theme="1"/>
       <name val="Verdana"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -134,19 +143,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -155,7 +167,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -164,13 +176,13 @@
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -179,9 +191,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -197,9 +213,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -237,7 +253,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -343,7 +359,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -485,7 +501,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -494,20 +510,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA4B462-8401-43D4-A97D-0B68FA77EED7}">
   <dimension ref="A1:H199"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.19921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.69921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.3984375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.36328125" style="9" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>11</v>
       </c>
@@ -530,7 +546,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>39492</v>
       </c>
@@ -553,7 +569,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>39514</v>
       </c>
@@ -576,7 +592,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>39547</v>
       </c>
@@ -599,7 +615,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>39568</v>
       </c>
@@ -622,7 +638,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>39612</v>
       </c>
@@ -645,7 +661,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>39644</v>
       </c>
@@ -668,7 +684,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>39679</v>
       </c>
@@ -691,7 +707,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>39708</v>
       </c>
@@ -714,7 +730,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>39728</v>
       </c>
@@ -737,7 +753,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>39752</v>
       </c>
@@ -760,7 +776,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>39773</v>
       </c>
@@ -783,7 +799,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>39784</v>
       </c>
@@ -806,7 +822,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>39801</v>
       </c>
@@ -829,7 +845,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>39835</v>
       </c>
@@ -852,7 +868,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>39889</v>
       </c>
@@ -875,7 +891,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>39910</v>
       </c>
@@ -898,7 +914,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>39933</v>
       </c>
@@ -921,7 +937,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>39955</v>
       </c>
@@ -944,7 +960,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>39980</v>
       </c>
@@ -967,7 +983,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>40009</v>
       </c>
@@ -990,7 +1006,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>40036</v>
       </c>
@@ -1013,7 +1029,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>40073</v>
       </c>
@@ -1036,7 +1052,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>40100</v>
       </c>
@@ -1059,7 +1075,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>40116</v>
       </c>
@@ -1082,7 +1098,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7">
       <c r="A26" s="5">
         <v>40137</v>
       </c>
@@ -1105,7 +1121,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7">
       <c r="A27" s="5">
         <v>40148</v>
       </c>
@@ -1125,7 +1141,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>40165</v>
       </c>
@@ -1148,7 +1164,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7">
       <c r="A29" s="5">
         <v>40204</v>
       </c>
@@ -1171,7 +1187,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7">
       <c r="A30" s="5">
         <v>40227</v>
       </c>
@@ -1194,7 +1210,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7">
       <c r="A31" s="5">
         <v>40254</v>
       </c>
@@ -1217,7 +1233,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7">
       <c r="A32" s="5">
         <v>40275</v>
       </c>
@@ -1240,7 +1256,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7">
       <c r="A33" s="5">
         <v>40298</v>
       </c>
@@ -1263,7 +1279,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:7">
       <c r="A34" s="5">
         <v>40308</v>
       </c>
@@ -1286,7 +1302,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:7">
       <c r="A35" s="5">
         <v>40319</v>
       </c>
@@ -1309,7 +1325,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7">
       <c r="A36" s="5">
         <v>40344</v>
       </c>
@@ -1332,7 +1348,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7">
       <c r="A37" s="5">
         <v>40374</v>
       </c>
@@ -1355,7 +1371,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7">
       <c r="A38" s="5">
         <v>40400</v>
       </c>
@@ -1378,7 +1394,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7">
       <c r="A39" s="5">
         <v>40420</v>
       </c>
@@ -1401,7 +1417,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7">
       <c r="A40" s="5">
         <v>40428</v>
       </c>
@@ -1424,7 +1440,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7">
       <c r="A41" s="5">
         <v>40456</v>
       </c>
@@ -1447,7 +1463,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:7">
       <c r="A42" s="5">
         <v>40479</v>
       </c>
@@ -1470,7 +1486,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7">
       <c r="A43" s="5">
         <v>40487</v>
       </c>
@@ -1493,7 +1509,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:7">
       <c r="A44" s="5">
         <v>40533</v>
       </c>
@@ -1516,7 +1532,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:7">
       <c r="A45" s="5">
         <v>40568</v>
       </c>
@@ -1539,7 +1555,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:7">
       <c r="A46" s="5">
         <v>40589</v>
       </c>
@@ -1562,7 +1578,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7">
       <c r="A47" s="5">
         <v>40616</v>
       </c>
@@ -1585,7 +1601,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7">
       <c r="A48" s="5">
         <v>40640</v>
       </c>
@@ -1608,7 +1624,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:7">
       <c r="A49" s="5">
         <v>40661</v>
       </c>
@@ -1631,7 +1647,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:7">
       <c r="A50" s="5">
         <v>40683</v>
       </c>
@@ -1654,7 +1670,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:7">
       <c r="A51" s="5">
         <v>40708</v>
       </c>
@@ -1677,7 +1693,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:7">
       <c r="A52" s="5">
         <v>40736</v>
       </c>
@@ -1700,7 +1716,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:7">
       <c r="A53" s="5">
         <v>40759</v>
       </c>
@@ -1723,7 +1739,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:7">
       <c r="A54" s="5">
         <v>40793</v>
       </c>
@@ -1746,7 +1762,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:7">
       <c r="A55" s="5">
         <v>40823</v>
       </c>
@@ -1769,7 +1785,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:7">
       <c r="A56" s="5">
         <v>40843</v>
       </c>
@@ -1792,7 +1808,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:7">
       <c r="A57" s="5">
         <v>40863</v>
       </c>
@@ -1815,7 +1831,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:7">
       <c r="A58" s="5">
         <v>40898</v>
       </c>
@@ -1838,7 +1854,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:7">
       <c r="A59" s="5">
         <v>40932</v>
       </c>
@@ -1861,7 +1877,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:7">
       <c r="A60" s="5">
         <v>40953</v>
       </c>
@@ -1884,7 +1900,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:7">
       <c r="A61" s="5">
         <v>40981</v>
       </c>
@@ -1907,7 +1923,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:7">
       <c r="A62" s="5">
         <v>41009</v>
       </c>
@@ -1930,7 +1946,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:7">
       <c r="A63" s="5">
         <v>41026</v>
       </c>
@@ -1953,7 +1969,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:7">
       <c r="A64" s="5">
         <v>41052</v>
       </c>
@@ -1976,7 +1992,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:7">
       <c r="A65" s="5">
         <v>41075</v>
       </c>
@@ -1999,7 +2015,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:7">
       <c r="A66" s="5">
         <v>41102</v>
       </c>
@@ -2022,7 +2038,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:7">
       <c r="A67" s="5">
         <v>41130</v>
       </c>
@@ -2045,7 +2061,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:7">
       <c r="A68" s="5">
         <v>41171</v>
       </c>
@@ -2068,7 +2084,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:7">
       <c r="A69" s="5">
         <v>41187</v>
       </c>
@@ -2091,7 +2107,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:7">
       <c r="A70" s="5">
         <v>41212</v>
       </c>
@@ -2114,7 +2130,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:7">
       <c r="A71" s="5">
         <v>41233</v>
       </c>
@@ -2137,7 +2153,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:7">
       <c r="A72" s="5">
         <v>41263</v>
       </c>
@@ -2160,7 +2176,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:7">
       <c r="A73" s="5">
         <v>41296</v>
       </c>
@@ -2183,7 +2199,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:7">
       <c r="A74" s="5">
         <v>41319</v>
       </c>
@@ -2206,7 +2222,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:7">
       <c r="A75" s="5">
         <v>41340</v>
       </c>
@@ -2229,7 +2245,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:7">
       <c r="A76" s="5">
         <v>41368</v>
       </c>
@@ -2252,7 +2268,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:7">
       <c r="A77" s="5">
         <v>41390</v>
       </c>
@@ -2275,7 +2291,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:7">
       <c r="A78" s="5">
         <v>41416</v>
       </c>
@@ -2298,7 +2314,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:7">
       <c r="A79" s="5">
         <v>41436</v>
       </c>
@@ -2321,7 +2337,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:7">
       <c r="A80" s="5">
         <v>41466</v>
       </c>
@@ -2344,7 +2360,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:7">
       <c r="A81" s="5">
         <v>41494</v>
       </c>
@@ -2367,7 +2383,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:7">
       <c r="A82" s="5">
         <v>41522</v>
       </c>
@@ -2390,7 +2406,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:7">
       <c r="A83" s="5">
         <v>41551</v>
       </c>
@@ -2413,7 +2429,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:7">
       <c r="A84" s="5">
         <v>41578</v>
       </c>
@@ -2436,7 +2452,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:7">
       <c r="A85" s="5">
         <v>41599</v>
       </c>
@@ -2459,7 +2475,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:7">
       <c r="A86" s="5">
         <v>41628</v>
       </c>
@@ -2482,7 +2498,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:7">
       <c r="A87" s="5">
         <v>41661</v>
       </c>
@@ -2505,7 +2521,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:7">
       <c r="A88" s="5">
         <v>41688</v>
       </c>
@@ -2528,7 +2544,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:7">
       <c r="A89" s="5">
         <v>41709</v>
       </c>
@@ -2551,7 +2567,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:7">
       <c r="A90" s="5">
         <v>41737</v>
       </c>
@@ -2574,7 +2590,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:7">
       <c r="A91" s="5">
         <v>41759</v>
       </c>
@@ -2597,7 +2613,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:7">
       <c r="A92" s="5">
         <v>41780</v>
       </c>
@@ -2620,7 +2636,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:7">
       <c r="A93" s="5">
         <v>41803</v>
       </c>
@@ -2643,7 +2659,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:7">
       <c r="A94" s="5">
         <v>41835</v>
       </c>
@@ -2666,7 +2682,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:7">
       <c r="A95" s="5">
         <v>41859</v>
       </c>
@@ -2689,7 +2705,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:7">
       <c r="A96" s="5">
         <v>41886</v>
       </c>
@@ -2712,7 +2728,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:7">
       <c r="A97" s="5">
         <v>41919</v>
       </c>
@@ -2735,7 +2751,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:7">
       <c r="A98" s="5">
         <v>41943</v>
       </c>
@@ -2758,7 +2774,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:7">
       <c r="A99" s="5">
         <v>41962</v>
       </c>
@@ -2781,7 +2797,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:7">
       <c r="A100" s="5">
         <v>41992</v>
       </c>
@@ -2804,7 +2820,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:7">
       <c r="A101" s="5">
         <v>42025</v>
       </c>
@@ -2827,7 +2843,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:7">
       <c r="A102" s="5">
         <v>42053</v>
       </c>
@@ -2850,7 +2866,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:7">
       <c r="A103" s="5">
         <v>42080</v>
       </c>
@@ -2873,7 +2889,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:7">
       <c r="A104" s="5">
         <v>42102</v>
       </c>
@@ -2896,7 +2912,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:7">
       <c r="A105" s="5">
         <v>42124</v>
       </c>
@@ -2919,7 +2935,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:7">
       <c r="A106" s="5">
         <v>42146</v>
       </c>
@@ -2942,7 +2958,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:7">
       <c r="A107" s="5">
         <v>42174</v>
       </c>
@@ -2965,7 +2981,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:7">
       <c r="A108" s="5">
         <v>42200</v>
       </c>
@@ -2988,7 +3004,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:7">
       <c r="A109" s="5">
         <v>42223</v>
       </c>
@@ -3011,7 +3027,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:7">
       <c r="A110" s="5">
         <v>42262</v>
       </c>
@@ -3034,7 +3050,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:7">
       <c r="A111" s="5">
         <v>42284</v>
       </c>
@@ -3057,7 +3073,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:7">
       <c r="A112" s="5">
         <v>42307</v>
       </c>
@@ -3080,7 +3096,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:7">
       <c r="A113" s="5">
         <v>42327</v>
       </c>
@@ -3103,7 +3119,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:7">
       <c r="A114" s="5">
         <v>42356</v>
       </c>
@@ -3126,7 +3142,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:7">
       <c r="A115" s="5">
         <v>42398</v>
       </c>
@@ -3149,7 +3165,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:7">
       <c r="A116" s="5">
         <v>42444</v>
       </c>
@@ -3172,7 +3188,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:7">
       <c r="A117" s="5">
         <v>42488</v>
       </c>
@@ -3195,7 +3211,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:7">
       <c r="A118" s="5">
         <v>42537</v>
       </c>
@@ -3218,7 +3234,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:7">
       <c r="A119" s="5">
         <v>42580</v>
       </c>
@@ -3241,7 +3257,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:7">
       <c r="A120" s="5">
         <v>42634</v>
       </c>
@@ -3264,7 +3280,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:7">
       <c r="A121" s="5">
         <v>42675</v>
       </c>
@@ -3287,7 +3303,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:7">
       <c r="A122" s="5">
         <v>42724</v>
       </c>
@@ -3310,7 +3326,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:7">
       <c r="A123" s="5">
         <v>42766</v>
       </c>
@@ -3333,7 +3349,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:7">
       <c r="A124" s="5">
         <v>42810</v>
       </c>
@@ -3356,7 +3372,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:7">
       <c r="A125" s="5">
         <v>42852</v>
       </c>
@@ -3379,7 +3395,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:7">
       <c r="A126" s="5">
         <v>42902</v>
       </c>
@@ -3402,7 +3418,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:7">
       <c r="A127" s="5">
         <v>42936</v>
       </c>
@@ -3425,7 +3441,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:7">
       <c r="A128" s="5">
         <v>42999</v>
       </c>
@@ -3448,7 +3464,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:7">
       <c r="A129" s="5">
         <v>43039</v>
       </c>
@@ -3471,7 +3487,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:7">
       <c r="A130" s="5">
         <v>43090</v>
       </c>
@@ -3494,7 +3510,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:7">
       <c r="A131" s="5">
         <v>43123</v>
       </c>
@@ -3517,7 +3533,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:7">
       <c r="A132" s="5">
         <v>43168</v>
       </c>
@@ -3540,7 +3556,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:7">
       <c r="A133" s="5">
         <v>43217</v>
       </c>
@@ -3563,7 +3579,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:7">
       <c r="A134" s="5">
         <v>43266</v>
       </c>
@@ -3586,7 +3602,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:7">
       <c r="A135" s="5">
         <v>43312</v>
       </c>
@@ -3609,7 +3625,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:7">
       <c r="A136" s="5">
         <v>43362</v>
       </c>
@@ -3632,7 +3648,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:7">
       <c r="A137" s="5">
         <v>43404</v>
       </c>
@@ -3655,7 +3671,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:7">
       <c r="A138" s="5">
         <v>43454</v>
       </c>
@@ -3678,7 +3694,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:7">
       <c r="A139" s="5">
         <v>43488</v>
       </c>
@@ -3701,7 +3717,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:7">
       <c r="A140" s="5">
         <v>43539</v>
       </c>
@@ -3724,7 +3740,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:7">
       <c r="A141" s="5">
         <v>43580</v>
       </c>
@@ -3747,7 +3763,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:7">
       <c r="A142" s="5">
         <v>43636</v>
       </c>
@@ -3770,7 +3786,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:7">
       <c r="A143" s="5">
         <v>43676</v>
       </c>
@@ -3793,7 +3809,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:7">
       <c r="A144" s="5">
         <v>43727</v>
       </c>
@@ -3816,7 +3832,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:7">
       <c r="A145" s="5">
         <v>43769</v>
       </c>
@@ -3839,7 +3855,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:7">
       <c r="A146" s="5">
         <v>43818</v>
       </c>
@@ -3862,7 +3878,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:7">
       <c r="A147" s="5">
         <v>43851</v>
       </c>
@@ -3885,7 +3901,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:7">
       <c r="A148" s="5">
         <v>43906</v>
       </c>
@@ -3908,7 +3924,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:7">
       <c r="A149" s="5">
         <v>43948</v>
       </c>
@@ -3931,7 +3947,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:7">
       <c r="A150" s="5">
         <v>43973</v>
       </c>
@@ -3951,7 +3967,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:7">
       <c r="A151" s="5">
         <v>43998</v>
       </c>
@@ -3971,7 +3987,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:7">
       <c r="A152" s="5">
         <v>44027</v>
       </c>
@@ -3994,7 +4010,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:7">
       <c r="A153" s="5">
         <v>44091</v>
       </c>
@@ -4017,7 +4033,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:7">
       <c r="A154" s="5">
         <v>44133</v>
       </c>
@@ -4040,7 +4056,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:7">
       <c r="A155" s="5">
         <v>44183</v>
       </c>
@@ -4063,7 +4079,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:7">
       <c r="A156" s="5">
         <v>44217</v>
       </c>
@@ -4086,7 +4102,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:7">
       <c r="A157" s="5">
         <v>44274</v>
       </c>
@@ -4109,7 +4125,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:7">
       <c r="A158" s="5">
         <v>44313</v>
       </c>
@@ -4132,7 +4148,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:7">
       <c r="A159" s="5">
         <v>44365</v>
       </c>
@@ -4155,7 +4171,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:7">
       <c r="A160" s="5">
         <v>44393</v>
       </c>
@@ -4178,7 +4194,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:7">
       <c r="A161" s="5">
         <v>44461</v>
       </c>
@@ -4198,7 +4214,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:7">
       <c r="A162" s="5">
         <v>44497</v>
       </c>
@@ -4221,7 +4237,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:7">
       <c r="A163" s="5">
         <v>44547</v>
       </c>
@@ -4244,7 +4260,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:7">
       <c r="A164" s="5">
         <v>44579</v>
       </c>
@@ -4267,7 +4283,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:7">
       <c r="A165" s="5">
         <v>44638</v>
       </c>
@@ -4290,7 +4306,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:7">
       <c r="A166" s="5">
         <v>44679</v>
       </c>
@@ -4313,7 +4329,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:7">
       <c r="A167" s="5">
         <v>44729</v>
       </c>
@@ -4336,7 +4352,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:7">
       <c r="A168" s="5">
         <v>44729</v>
       </c>
@@ -4356,7 +4372,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:7">
       <c r="A169" s="5">
         <v>44763</v>
       </c>
@@ -4379,7 +4395,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:7">
       <c r="A170" s="5">
         <v>44826</v>
       </c>
@@ -4402,7 +4418,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:7">
       <c r="A171" s="5">
         <v>44862</v>
       </c>
@@ -4425,7 +4441,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:7">
       <c r="A172" s="5">
         <v>44915</v>
       </c>
@@ -4448,7 +4464,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:7">
       <c r="A173" s="5">
         <v>44944</v>
       </c>
@@ -4471,7 +4487,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:7">
       <c r="A174" s="5">
         <v>44995</v>
       </c>
@@ -4494,7 +4510,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:7">
       <c r="A175" s="5">
         <v>45044</v>
       </c>
@@ -4517,7 +4533,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:7">
       <c r="A176" s="5">
         <v>45093</v>
       </c>
@@ -4540,7 +4556,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:7">
       <c r="A177" s="5">
         <v>45135</v>
       </c>
@@ -4563,7 +4579,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:7">
       <c r="A178" s="5">
         <v>45191</v>
       </c>
@@ -4586,7 +4602,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:7">
       <c r="A179" s="5">
         <v>45230</v>
       </c>
@@ -4609,7 +4625,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:7">
       <c r="A180" s="5">
         <v>45279</v>
       </c>
@@ -4632,7 +4648,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:7">
       <c r="A181" s="5">
         <v>45314</v>
       </c>
@@ -4655,7 +4671,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:7">
       <c r="A182" s="5">
         <v>45370</v>
       </c>
@@ -4678,7 +4694,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:7">
       <c r="A183" s="5">
         <v>45408</v>
       </c>
@@ -4701,7 +4717,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:7">
       <c r="A184" s="5">
         <v>45457</v>
       </c>
@@ -4724,7 +4740,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:7">
       <c r="A185" s="5">
         <v>45504</v>
       </c>
@@ -4747,7 +4763,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:7">
       <c r="A186" s="5">
         <v>45555</v>
       </c>
@@ -4770,7 +4786,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:7">
       <c r="A187" s="5">
         <v>45596</v>
       </c>
@@ -4793,7 +4809,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:7">
       <c r="A188" s="5">
         <v>45645</v>
       </c>
@@ -4816,7 +4832,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:7">
       <c r="A189" s="5">
         <v>45681</v>
       </c>
@@ -4839,7 +4855,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:7">
       <c r="A190" s="5">
         <v>45735</v>
       </c>
@@ -4862,7 +4878,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:7">
       <c r="A191" s="5">
         <v>45778</v>
       </c>
@@ -4885,7 +4901,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:7">
       <c r="A192" s="5">
         <v>45825</v>
       </c>
@@ -4908,7 +4924,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:7">
       <c r="A193" s="5">
         <v>45869</v>
       </c>
@@ -4931,7 +4947,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:7">
       <c r="A194" s="5">
         <v>45919</v>
       </c>
@@ -4954,7 +4970,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:7">
       <c r="A195" s="5">
         <v>45960</v>
       </c>
@@ -4977,7 +4993,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:7">
       <c r="A196" s="5">
         <v>46010</v>
       </c>
@@ -5000,7 +5016,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:7">
       <c r="A197" s="11">
         <v>46045</v>
       </c>
@@ -5023,7 +5039,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:7">
       <c r="A198" s="11">
         <v>46100</v>
       </c>
@@ -5046,7 +5062,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:7">
       <c r="A199" s="11">
         <v>46140</v>
       </c>
@@ -5079,20 +5095,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB9E5B25-827A-49DC-A0E2-CBBE95A45320}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
@@ -5102,6 +5118,9 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{FB882056-553D-4A34-A8A0-F19A5A229BE0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>